--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-10" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-11" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-11" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-12" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-12" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-13" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-13" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-14" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-14" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-15" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-15" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-16" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-16" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-17" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-17" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-18" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-18" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-19" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-19" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-20" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -583,7 +583,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
+          <t xml:space="preserve">HTTP 520 &lt;none&gt;</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-20" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-21" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -583,7 +583,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 520 &lt;none&gt;</t>
+          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-21" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-22" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-22" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-23" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-23" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-24" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-24" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-25" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-25" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-26" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">scanned=0 title_hits=0 in_24h=0 (0.1s)</t>
+          <t xml:space="preserve">scanned=0 title_hits=0 in_24h=0 (0.2s)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-26" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-27" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">scanned=0 title_hits=0 in_24h=0 (0.2s)</t>
+          <t xml:space="preserve">scanned=0 title_hits=0 in_24h=0 (0.1s)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-27" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-28" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -1378,103 +1378,103 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avidity Biosciences</t>
+          <t xml:space="preserve">Blueprint Medicines</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">no diagnostic</t>
+          <t xml:space="preserve">scanned=0 title_hits=0 in_24h=0 (0.1s)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/aviditybiosciences</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/blueprintmedicines</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Avidity%20Biosciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Blueprint%20Medicines%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Avidity%20Biosciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Blueprint%20Medicines%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Avidity%20Biosciences%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Blueprint%20Medicines%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cytokinetics</t>
+          <t xml:space="preserve">Avidity Biosciences</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 404 Not Found</t>
+          <t xml:space="preserve">no diagnostic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/cytokinetics</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/aviditybiosciences</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Cytokinetics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Avidity%20Biosciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Cytokinetics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Avidity%20Biosciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Cytokinetics%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Avidity%20Biosciences%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viking Therapeutics</t>
+          <t xml:space="preserve">Cytokinetics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">no diagnostic</t>
+          <t xml:space="preserve">HTTP 404 Not Found</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/vikingtherapeutics</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/cytokinetics</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Viking%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Cytokinetics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Viking%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Cytokinetics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Viking%20Therapeutics%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Cytokinetics%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">89bio</t>
+          <t xml:space="preserve">Viking Therapeutics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1484,29 +1484,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/89bio</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/vikingtherapeutics</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=89bio%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Viking%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%2089bio%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Viking%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=89bio%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Viking%20Therapeutics%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structure Therapeutics</t>
+          <t xml:space="preserve">89bio</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1516,29 +1516,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/structuretherapeutics</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/89bio</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Structure%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=89bio%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Structure%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%2089bio%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Structure%20Therapeutics%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=89bio%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Replimune</t>
+          <t xml:space="preserve">Structure Therapeutics</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1548,29 +1548,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/replimune</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/structuretherapeutics</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Replimune%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Structure%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Replimune%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Structure%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Replimune%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Structure%20Therapeutics%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krystal Biotech</t>
+          <t xml:space="preserve">Replimune</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1580,29 +1580,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/krystalbiotech</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/replimune</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Krystal%20Biotech%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Replimune%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Krystal%20Biotech%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Replimune%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Krystal%20Biotech%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Replimune%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">PTC Therapeutics</t>
+          <t xml:space="preserve">Krystal Biotech</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1612,29 +1612,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/ptcbio</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/krystalbiotech</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=PTC%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Krystal%20Biotech%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20PTC%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Krystal%20Biotech%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=PTC%20Therapeutics%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Krystal%20Biotech%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travere Therapeutics</t>
+          <t xml:space="preserve">PTC Therapeutics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1644,29 +1644,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/traveretherapeutics</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/ptcbio</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Travere%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=PTC%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Travere%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20PTC%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Travere%20Therapeutics%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=PTC%20Therapeutics%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caribou Biosciences</t>
+          <t xml:space="preserve">Travere Therapeutics</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1676,29 +1676,29 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/cariboubiosciences</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/traveretherapeutics</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Caribou%20Biosciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Travere%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Caribou%20Biosciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Travere%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Caribou%20Biosciences%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Travere%20Therapeutics%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allogene Therapeutics</t>
+          <t xml:space="preserve">Caribou Biosciences</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1708,93 +1708,93 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/allogene</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/cariboubiosciences</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Allogene%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Caribou%20Biosciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Allogene%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Caribou%20Biosciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Allogene%20Therapeutics%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Caribou%20Biosciences%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arcellx</t>
+          <t xml:space="preserve">Allogene Therapeutics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 404 Not Found</t>
+          <t xml:space="preserve">no diagnostic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/arcellx</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/allogene</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Arcellx%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Allogene%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Arcellx%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Allogene%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Arcellx%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Allogene%20Therapeutics%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sana Biotechnology</t>
+          <t xml:space="preserve">Arcellx</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">no diagnostic</t>
+          <t xml:space="preserve">HTTP 404 Not Found</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/sanabiotechnology</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/arcellx</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Sana%20Biotechnology%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Arcellx%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Sana%20Biotechnology%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Arcellx%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Sana%20Biotechnology%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Arcellx%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rocket Pharmaceuticals</t>
+          <t xml:space="preserve">Sana Biotechnology</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1804,29 +1804,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/rocketpharma</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/sanabiotechnology</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Rocket%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Sana%20Biotechnology%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Rocket%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Sana%20Biotechnology%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Rocket%20Pharmaceuticals%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Sana%20Biotechnology%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ultragenyx Pharmaceutical</t>
+          <t xml:space="preserve">Rocket Pharmaceuticals</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1836,189 +1836,189 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/ultragenyx</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/rocketpharma</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Ultragenyx%20Pharmaceutical%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Rocket%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Ultragenyx%20Pharmaceutical%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Rocket%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Ultragenyx%20Pharmaceutical%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Rocket%20Pharmaceuticals%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generation Bio</t>
+          <t xml:space="preserve">Ultragenyx Pharmaceutical</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 404 Not Found</t>
+          <t xml:space="preserve">no diagnostic</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/generationbio</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/ultragenyx</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Generation%20Bio%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Ultragenyx%20Pharmaceutical%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Generation%20Bio%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Ultragenyx%20Pharmaceutical%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Generation%20Bio%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Ultragenyx%20Pharmaceutical%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Voyager Therapeutics</t>
+          <t xml:space="preserve">Generation Bio</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">scanned=0 title_hits=0 in_24h=0 (0.1s)</t>
+          <t xml:space="preserve">HTTP 404 Not Found</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/voyagertherapeutics</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/generationbio</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Voyager%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Generation%20Bio%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Voyager%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Generation%20Bio%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Voyager%20Therapeutics%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Generation%20Bio%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wave Life Sciences</t>
+          <t xml:space="preserve">Voyager Therapeutics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">no diagnostic</t>
+          <t xml:space="preserve">scanned=0 title_hits=0 in_24h=0 (0.1s)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/wavelifesciences</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/voyagertherapeutics</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Wave%20Life%20Sciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Voyager%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Wave%20Life%20Sciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Voyager%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Wave%20Life%20Sciences%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Voyager%20Therapeutics%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arrowhead Pharmaceuticals</t>
+          <t xml:space="preserve">Wave Life Sciences</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
+          <t xml:space="preserve">no diagnostic</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://arrowheadpharma.wd1.myworkdayjobs.com/Arrowhead_Careers</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/wavelifesciences</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Arrowhead%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Wave%20Life%20Sciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Arrowhead%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Wave%20Life%20Sciences%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Arrowhead%20Pharmaceuticals%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Wave%20Life%20Sciences%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vir Biotechnology</t>
+          <t xml:space="preserve">Arrowhead Pharmaceuticals</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">no diagnostic</t>
+          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/virbiotechnology</t>
+          <t xml:space="preserve">https://arrowheadpharma.wd1.myworkdayjobs.com/Arrowhead_Careers</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Vir%20Biotechnology%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Arrowhead%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Vir%20Biotechnology%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Arrowhead%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Vir%20Biotechnology%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Arrowhead%20Pharmaceuticals%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denali Therapeutics</t>
+          <t xml:space="preserve">Vir Biotechnology</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2028,29 +2028,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/denalitherapeutics</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/virbiotechnology</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Denali%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Vir%20Biotechnology%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Denali%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Vir%20Biotechnology%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Denali%20Therapeutics%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Vir%20Biotechnology%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Annexon</t>
+          <t xml:space="preserve">Denali Therapeutics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2060,29 +2060,29 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/annexon</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/denalitherapeutics</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Annexon%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Denali%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Annexon%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Denali%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Annexon%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Denali%20Therapeutics%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arcutis Biotherapeutics</t>
+          <t xml:space="preserve">Annexon</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2092,29 +2092,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/arcutis</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/annexon</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Arcutis%20Biotherapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Annexon%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Arcutis%20Biotherapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Annexon%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Arcutis%20Biotherapeutics%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Annexon%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vera Therapeutics</t>
+          <t xml:space="preserve">Arcutis Biotherapeutics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2124,29 +2124,29 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/veratherapeutics</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/arcutis</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Vera%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Arcutis%20Biotherapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Vera%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Arcutis%20Biotherapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Vera%20Therapeutics%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Arcutis%20Biotherapeutics%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genmab</t>
+          <t xml:space="preserve">Vera Therapeutics</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2156,29 +2156,29 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://genmab.wd3.myworkdayjobs.com/GenmabCareers</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/veratherapeutics</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Genmab%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Vera%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Genmab%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Vera%20Therapeutics%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Genmab%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Vera%20Therapeutics%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">argenx</t>
+          <t xml:space="preserve">Genmab</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2188,61 +2188,61 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://argenx.wd3.myworkdayjobs.com/argenxcareers</t>
+          <t xml:space="preserve">https://genmab.wd3.myworkdayjobs.com/GenmabCareers</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=argenx%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Genmab%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20argenx%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Genmab%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=argenx%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Genmab%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ascendis Pharma</t>
+          <t xml:space="preserve">argenx</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
+          <t xml:space="preserve">no diagnostic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://ascendispharma.wd5.myworkdayjobs.com/Ascendis</t>
+          <t xml:space="preserve">https://argenx.wd3.myworkdayjobs.com/argenxcareers</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Ascendis%20Pharma%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=argenx%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Ascendis%20Pharma%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20argenx%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Ascendis%20Pharma%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=argenx%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">BeOne Medicines (BeiGene)</t>
+          <t xml:space="preserve">Ascendis Pharma</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2252,29 +2252,29 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://beigene.wd1.myworkdayjobs.com/BeiGene_External_Career_Site</t>
+          <t xml:space="preserve">https://ascendispharma.wd5.myworkdayjobs.com/Ascendis</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=BeOne%20Medicines%20%28BeiGene%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Ascendis%20Pharma%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20BeOne%20Medicines%20%28BeiGene%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Ascendis%20Pharma%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=BeOne%20Medicines%20%28BeiGene%29%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Ascendis%20Pharma%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teva Pharmaceuticals</t>
+          <t xml:space="preserve">BeOne Medicines (BeiGene)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2284,29 +2284,29 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://teva.wd3.myworkdayjobs.com/tevapharmaceuticalsexternalcareersite</t>
+          <t xml:space="preserve">https://beigene.wd1.myworkdayjobs.com/BeiGene_External_Career_Site</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Teva%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=BeOne%20Medicines%20%28BeiGene%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Teva%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20BeOne%20Medicines%20%28BeiGene%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Teva%20Pharmaceuticals%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=BeOne%20Medicines%20%28BeiGene%29%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alkermes</t>
+          <t xml:space="preserve">Teva Pharmaceuticals</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2316,29 +2316,29 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://alkermes.wd1.myworkdayjobs.com/External</t>
+          <t xml:space="preserve">https://teva.wd3.myworkdayjobs.com/tevapharmaceuticalsexternalcareersite</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Alkermes%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Teva%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Alkermes%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Teva%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Alkermes%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Teva%20Pharmaceuticals%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supernus Pharmaceuticals</t>
+          <t xml:space="preserve">Alkermes</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2348,93 +2348,93 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://supernus.wd1.myworkdayjobs.com/Supernus_External_Career_Site</t>
+          <t xml:space="preserve">https://alkermes.wd1.myworkdayjobs.com/External</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Supernus%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Alkermes%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Supernus%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Alkermes%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Supernus%20Pharmaceuticals%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Alkermes%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">ICON plc</t>
+          <t xml:space="preserve">Supernus Pharmaceuticals</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">no diagnostic</t>
+          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://icon.wd3.myworkdayjobs.com/iconplc</t>
+          <t xml:space="preserve">https://supernus.wd1.myworkdayjobs.com/Supernus_External_Career_Site</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=ICON%20plc%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Supernus%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20ICON%20plc%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Supernus%20Pharmaceuticals%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=ICON%20plc%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Supernus%20Pharmaceuticals%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charles River Laboratories</t>
+          <t xml:space="preserve">ICON plc</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
+          <t xml:space="preserve">no diagnostic</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://crl.wd1.myworkdayjobs.com/CRL_Careers</t>
+          <t xml:space="preserve">https://icon.wd3.myworkdayjobs.com/iconplc</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Charles%20River%20Laboratories%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=ICON%20plc%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Charles%20River%20Laboratories%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20ICON%20plc%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Charles%20River%20Laboratories%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=ICON%20plc%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medpace</t>
+          <t xml:space="preserve">Charles River Laboratories</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2444,29 +2444,29 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://medpace.wd5.myworkdayjobs.com/External</t>
+          <t xml:space="preserve">https://crl.wd1.myworkdayjobs.com/CRL_Careers</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Medpace%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Charles%20River%20Laboratories%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Medpace%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Charles%20River%20Laboratories%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Medpace%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Charles%20River%20Laboratories%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parexel</t>
+          <t xml:space="preserve">Medpace</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2476,29 +2476,29 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://parexel.wd3.myworkdayjobs.com/parexel</t>
+          <t xml:space="preserve">https://medpace.wd5.myworkdayjobs.com/External</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Parexel%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Medpace%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Parexel%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Medpace%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Parexel%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Medpace%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syneos Health</t>
+          <t xml:space="preserve">Parexel</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2508,61 +2508,61 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://syneoshealth.wd1.myworkdayjobs.com/syneoshealth</t>
+          <t xml:space="preserve">https://parexel.wd3.myworkdayjobs.com/parexel</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Syneos%20Health%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Parexel%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Syneos%20Health%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Parexel%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Syneos%20Health%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Parexel%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermo Fisher Scientific (incl. PPD)</t>
+          <t xml:space="preserve">Syneos Health</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">no diagnostic</t>
+          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://thermofisher.wd5.myworkdayjobs.com/thermofisher_career</t>
+          <t xml:space="preserve">https://syneoshealth.wd1.myworkdayjobs.com/syneoshealth</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Thermo%20Fisher%20Scientific%20%28incl.%20PPD%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Syneos%20Health%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Thermo%20Fisher%20Scientific%20%28incl.%20PPD%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Syneos%20Health%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Thermo%20Fisher%20Scientific%20%28incl.%20PPD%29%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Syneos%20Health%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veristat</t>
+          <t xml:space="preserve">Thermo Fisher Scientific (incl. PPD)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2572,93 +2572,93 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/veristat</t>
+          <t xml:space="preserve">https://thermofisher.wd5.myworkdayjobs.com/thermofisher_career</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Veristat%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Thermo%20Fisher%20Scientific%20%28incl.%20PPD%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Veristat%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Thermo%20Fisher%20Scientific%20%28incl.%20PPD%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Veristat%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Thermo%20Fisher%20Scientific%20%28incl.%20PPD%29%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">BioAgilytix</t>
+          <t xml:space="preserve">Veristat</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
+          <t xml:space="preserve">no diagnostic</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://bioagilytix.wd1.myworkdayjobs.com/bioagilytix</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/veristat</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=BioAgilytix%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Veristat%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20BioAgilytix%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Veristat%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=BioAgilytix%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Veristat%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worldwide Clinical Trials</t>
+          <t xml:space="preserve">BioAgilytix</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">no diagnostic</t>
+          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/worldwide</t>
+          <t xml:space="preserve">https://bioagilytix.wd1.myworkdayjobs.com/bioagilytix</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Worldwide%20Clinical%20Trials%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=BioAgilytix%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Worldwide%20Clinical%20Trials%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20BioAgilytix%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Worldwide%20Clinical%20Trials%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=BioAgilytix%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Premier Research</t>
+          <t xml:space="preserve">Worldwide Clinical Trials</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2668,29 +2668,29 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://boards.greenhouse.io/premierresearch</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/worldwide</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Premier%20Research%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Worldwide%20Clinical%20Trials%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Premier%20Research%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Worldwide%20Clinical%20Trials%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Premier%20Research%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Worldwide%20Clinical%20Trials%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lonza</t>
+          <t xml:space="preserve">Premier Research</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2700,29 +2700,29 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://lonza.wd3.myworkdayjobs.com/lonza_external_careers</t>
+          <t xml:space="preserve">https://boards.greenhouse.io/premierresearch</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Lonza%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Premier%20Research%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Lonza%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Premier%20Research%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Lonza%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Premier%20Research%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catalent</t>
+          <t xml:space="preserve">Lonza</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2732,125 +2732,125 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://catalent.wd1.myworkdayjobs.com/Catalent_Careers</t>
+          <t xml:space="preserve">https://lonza.wd3.myworkdayjobs.com/lonza_external_careers</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Catalent%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Lonza%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Catalent%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Lonza%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Catalent%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Lonza%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elanco Animal Health</t>
+          <t xml:space="preserve">Catalent</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
+          <t xml:space="preserve">no diagnostic</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://elanco.wd1.myworkdayjobs.com/Elanco_Careers</t>
+          <t xml:space="preserve">https://catalent.wd1.myworkdayjobs.com/Catalent_Careers</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Elanco%20Animal%20Health%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Catalent%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Elanco%20Animal%20Health%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Catalent%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Elanco%20Animal%20Health%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Catalent%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organon</t>
+          <t xml:space="preserve">Elanco Animal Health</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">no diagnostic</t>
+          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://organon.wd5.myworkdayjobs.com/OrganonCareers</t>
+          <t xml:space="preserve">https://elanco.wd1.myworkdayjobs.com/Elanco_Careers</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Organon%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Elanco%20Animal%20Health%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Organon%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Elanco%20Animal%20Health%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Organon%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Elanco%20Animal%20Health%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMD Serono (Merck KGaA)</t>
+          <t xml:space="preserve">Organon</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
+          <t xml:space="preserve">no diagnostic</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://merckgroup.wd3.myworkdayjobs.com/MerckGroup</t>
+          <t xml:space="preserve">https://organon.wd5.myworkdayjobs.com/OrganonCareers</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=EMD%20Serono%20%28Merck%20KGaA%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Organon%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20EMD%20Serono%20%28Merck%20KGaA%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Organon%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=EMD%20Serono%20%28Merck%20KGaA%29%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Organon%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">UCB</t>
+          <t xml:space="preserve">EMD Serono (Merck KGaA)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2860,29 +2860,29 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://ucb.wd3.myworkdayjobs.com/ucbcareers</t>
+          <t xml:space="preserve">https://merckgroup.wd3.myworkdayjobs.com/MerckGroup</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=UCB%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=EMD%20Serono%20%28Merck%20KGaA%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20UCB%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20EMD%20Serono%20%28Merck%20KGaA%29%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=UCB%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=EMD%20Serono%20%28Merck%20KGaA%29%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sumitomo Pharma America</t>
+          <t xml:space="preserve">UCB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2892,29 +2892,29 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://sumitomopharma.wd1.myworkdayjobs.com/SumitomoPharma_External_Career_Site</t>
+          <t xml:space="preserve">https://ucb.wd3.myworkdayjobs.com/ucbcareers</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Sumitomo%20Pharma%20America%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=UCB%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Sumitomo%20Pharma%20America%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20UCB%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Sumitomo%20Pharma%20America%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=UCB%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbeck</t>
+          <t xml:space="preserve">Sumitomo Pharma America</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2924,52 +2924,84 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://lundbeck.wd3.myworkdayjobs.com/External</t>
+          <t xml:space="preserve">https://sumitomopharma.wd1.myworkdayjobs.com/SumitomoPharma_External_Career_Site</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Lundbeck%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Sumitomo%20Pharma%20America%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Lundbeck%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Sumitomo%20Pharma%20America%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Lundbeck%20biostatistics</t>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Sumitomo%20Pharma%20America%20biostatistics</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundbeck</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://lundbeck.wd3.myworkdayjobs.com/External</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Lundbeck%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Lundbeck%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Lundbeck%20biostatistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ipsen</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 422 Unprocessable Entity</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t xml:space="preserve">https://ipsen.wd3.myworkdayjobs.com/Ipsencareers</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.linkedin.com/jobs/search/?keywords=Ipsen%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;f_TPR=r86400</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.google.com/search?q=site%3Alinkedin.com/jobs%20Ipsen%20biostatistics%20%28%22senior%20manager%22%20OR%20%22associate%20director%22%29&amp;tbs=qdr:d</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.biospace.com/jobs/?keywords=Ipsen%20biostatistics</t>
         </is>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-28" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-29" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-29" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-30" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>

--- a/daily-jobs/manual-check-latest.xlsx
+++ b/daily-jobs/manual-check-latest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Manual check 2026-10-30" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual check 2026-10-31" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
